--- a/WorkBot/refactor-experimental/data/orders/Coca-Cola/Coca-Cola_Downtown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Coca-Cola/Coca-Cola_Downtown_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Coca-Cola Bottles</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27.58</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Coca-Cola Zero Sugar Bottles</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="E3" t="n">
+        <v>26.46</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Core Power Protein - Chocolate</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>32.55</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>32.55</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="E4" t="n">
+        <v>32.55</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Diet Coke Bottles</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="E5" t="n">
+        <v>27.58</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Dr Pepper Bottles</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26.46</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Vitamin Water - XXX</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>16.07</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>16.07</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.07</v>
       </c>
     </row>
   </sheetData>
